--- a/output/pdf_financials_xlsx/VM.xlsx
+++ b/output/pdf_financials_xlsx/VM.xlsx
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.09446</v>
+        <v>-0.09446</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.001482</v>
+        <v>-0.001482</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.693198</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.09446</v>
+        <v>-0.09446</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.001482</v>
+        <v>-0.001482</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.693198</v>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.09446</v>
+        <v>-0.09446</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.001482</v>
+        <v>-0.001482</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.693198</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.8892</v>
+        <v>-1.8892</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.09446</v>
+        <v>-0.09446</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.001482</v>
+        <v>-0.001482</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.693198</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.09446</v>
+        <v>-0.09446</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.001482</v>
+        <v>-0.001482</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.693198</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.053219</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.053219</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.053219</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.043595</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.09446</v>
+        <v>-0.09446</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.001482</v>
@@ -5213,31 +5213,31 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.163652</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.53298</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.320998</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.173539</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.416395</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.280438</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.174721</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.165955</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.27002</v>
       </c>
     </row>
     <row r="119">
@@ -11894,7 +11894,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>0.053219</v>
       </c>
@@ -13657,7 +13661,11 @@
           <t>Exploration and evaluation expenditures (note 6)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -15899,7 +15907,11 @@
           <t>Exploration and evaluation expenditures (note 5)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -18581,7 +18593,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -19936,7 +19952,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -26419,13 +26439,13 @@
         </is>
       </c>
       <c r="E290" s="5" t="n">
-        <v>0.09446</v>
+        <v>-0.09446</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>0.001482</v>
+        <v>-0.001482</v>
       </c>
       <c r="G290" s="5" t="n">
-        <v>0.052323</v>
+        <v>-0.052323</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VM.xlsx
+++ b/output/pdf_financials_xlsx/VM.xlsx
@@ -5464,19 +5464,19 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004538</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008129000000000001</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008584</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014373</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016557</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -5504,19 +5504,19 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004538</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008129000000000001</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008584</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014373</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016557</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -6477,7 +6477,11 @@
           <t>Reclamation deposits (note 10)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -7717,7 +7721,11 @@
           <t>Reclamation deposits (note 9)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -8135,7 +8143,11 @@
           <t>Reclamation deposits (note 7)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -9533,7 +9545,11 @@
           <t>Reclamation deposits (note 7)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15483,7 +15499,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -16972,7 +16992,11 @@
           <t>Finance lease payments (note 4)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -18102,7 +18126,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VM.xlsx
+++ b/output/pdf_financials_xlsx/VM.xlsx
@@ -671,7 +671,7 @@
         <v>0.022306</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.143217</v>
+        <v>0.462688</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.125869</v>
@@ -791,7 +791,7 @@
         <v>0.022306</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.143217</v>
+        <v>0.462688</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.125869</v>
@@ -831,7 +831,7 @@
         <v>-0.554893</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.143217</v>
+        <v>-0.462688</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.125869</v>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.000935</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.069868</v>
+        <v>0.070803</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.06916700000000001</v>
@@ -4939,10 +4939,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006443</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001829</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -5897,10 +5897,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006443</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001829</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -13259,7 +13259,11 @@
           <t>Deposit private placement (note 7)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -17635,7 +17639,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -18552,7 +18560,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -19126,7 +19138,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -21278,7 +21294,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E217" s="5" t="n">
         <v>0.000935</v>
       </c>
@@ -24234,7 +24254,11 @@
           <t>Wages, benefits, director fees (note 6)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
